--- a/data/wedding-data.xlsx
+++ b/data/wedding-data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="95">
   <si>
     <t>key</t>
   </si>
@@ -31,7 +31,7 @@
     <t>weddingDate</t>
   </si>
   <si>
-    <t>2027-01-23T18:00:00-03:00</t>
+    <t>2027-01-23T21:00:00.000Z</t>
   </si>
   <si>
     <t>churchMapsUrl</t>
@@ -40,6 +40,12 @@
     <t>https://maps.app.goo.gl/Mt6wwARimRkpqReV7?g_st=iw</t>
   </si>
   <si>
+    <t>notices</t>
+  </si>
+  <si>
+    <t>[{"id":"confirmar-presenca","title":"Confirme sua presença","text":"Responda o quanto antes para nos ajudar na organização."},{"id":"pontualidade","title":"Pontualidade é essencial","text":"Chegar atrasado pode atrapalhar a cerimônia."},{"id":"celular-silencioso","title":"Silencie o celular","text":"Evite toques e notificações durante a cerimônia."}]</t>
+  </si>
+  <si>
     <t>audioUrl</t>
   </si>
   <si>
@@ -100,13 +106,22 @@
     <t>updatedAt</t>
   </si>
   <si>
-    <t>rsvp_607bdfb1-6276-4392-a23d-677192368fbd</t>
-  </si>
-  <si>
-    <t>Teste Codex</t>
-  </si>
-  <si>
-    <t>2026-07-18T01:29:55.190Z</t>
+    <t>rsvp_6aeff494-0809-4776-be46-65464acfcc69</t>
+  </si>
+  <si>
+    <t>Janiel</t>
+  </si>
+  <si>
+    <t>2026-07-18T12:08:07.959Z</t>
+  </si>
+  <si>
+    <t>rsvp_a20b2b69-a1e3-4bd0-8bf2-3aead9370186</t>
+  </si>
+  <si>
+    <t>Lina</t>
+  </si>
+  <si>
+    <t>2026-08-15T13:46:01.738Z</t>
   </si>
   <si>
     <t>imagePath</t>
@@ -118,6 +133,9 @@
     <t>sortOrder</t>
   </si>
   <si>
+    <t>quantity</t>
+  </si>
+  <si>
     <t>isActive</t>
   </si>
   <si>
@@ -127,13 +145,34 @@
     <t>Air fryer</t>
   </si>
   <si>
+    <t>/uploads/gifts/air-fryer-1.png</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-07-18T01:22:19.695Z</t>
+  </si>
+  <si>
+    <t>2026-08-15T13:33:01.063Z</t>
+  </si>
+  <si>
+    <t>gift_75b2949b-36f8-4c5d-8d1c-a588728303c0</t>
+  </si>
+  <si>
+    <t>Teste</t>
+  </si>
+  <si>
     <t>/images/gift-placeholder.svg</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-07-18T01:22:19.695Z</t>
+    <t>Der preferência a cores claras</t>
+  </si>
+  <si>
+    <t>2026-08-15T13:32:43.390Z</t>
+  </si>
+  <si>
+    <t>2026-08-15T13:45:01.380Z</t>
   </si>
   <si>
     <t>jogo-de-panelas-2</t>
@@ -254,6 +293,12 @@
   </si>
   <si>
     <t>ownerTokenHash</t>
+  </si>
+  <si>
+    <t>guestName</t>
+  </si>
+  <si>
+    <t>accessToken</t>
   </si>
 </sst>
 </file>
@@ -630,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -725,6 +770,14 @@
         <v>21</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -733,7 +786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -745,42 +798,62 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -791,562 +864,654 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="8" width="22" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>39</v>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
+      <c r="G3" t="b">
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="I3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6">
         <v>4</v>
       </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8">
         <v>6</v>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9">
         <v>7</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9">
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10">
         <v>8</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11">
         <v>9</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11">
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12">
         <v>10</v>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12">
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13">
         <v>11</v>
       </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13">
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14">
         <v>12</v>
       </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15">
         <v>13</v>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15">
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16">
         <v>14</v>
       </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16">
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17">
         <v>15</v>
       </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17">
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18">
         <v>16</v>
       </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>39</v>
-      </c>
-      <c r="H17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19">
         <v>17</v>
       </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20">
         <v>18</v>
       </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20">
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21">
         <v>19</v>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21">
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22">
         <v>20</v>
       </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>39</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1357,29 +1522,41 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
-    <col min="4" max="5" width="22" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
